--- a/backend/app/nakladna_template.xlsx
+++ b/backend/app/nakladna_template.xlsx
@@ -12,16 +12,6 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="bookkeepingInv440_25">Накладна440_25!$A$54</definedName>
-    <definedName name="ContentInvAdd440_25">Накладна440_25!$L$5</definedName>
-    <definedName name="DateWOff">'[1]Акт списання'!$L$2</definedName>
-    <definedName name="Dislocation">[1]!Таблиця4[Місце розташування]</definedName>
-    <definedName name="InvFields1">[1]!tbInv431[[2]:[5]]</definedName>
-    <definedName name="InvFields2">[1]!tbInv431[7]</definedName>
-    <definedName name="listContentAdd">[1]!Таблиця16[Тип операції детальний]</definedName>
-    <definedName name="lPeoples">[1]!Таблиця6[Для пошуку]</definedName>
-    <definedName name="NumberInv440_57">'[1]Розд(З)Відом д57'!$Q$5</definedName>
-    <definedName name="typeOperation">[1]!Таблиця8[Типи операції]</definedName>
     <definedName name="allCountInv440_25" localSheetId="0">Накладна440_25!$C$29</definedName>
     <definedName name="allSumInv440_25" localSheetId="0">Накладна440_25!$A$31</definedName>
     <definedName name="basis440_25" localSheetId="0">Накладна440_25!$I$13</definedName>
@@ -41,7 +31,7 @@
     <definedName name="toUnitInv440_25" localSheetId="0">Накладна440_25!$I$15</definedName>
     <definedName name="typeDocInv440_25" localSheetId="0">Накладна440_25!$C$7</definedName>
     <definedName name="typeOperation" localSheetId="0">[1]!Таблиця8[Типи операції]</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Накладна440_25'!$A$1:$J$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Накладна440_25'!$A$1:$J$55</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
